--- a/Tile_Overview.xlsx
+++ b/Tile_Overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\_Git\Boardgames\Elden Ring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\_Git\Boardgames\Elden Ring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE984411-0C59-4FA4-BDB1-1B0F7C2F47D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEA11EC-7A68-4AEE-923B-E8792AA4EE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="4185" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Number of Tiles</t>
   </si>
@@ -93,13 +93,40 @@
   </si>
   <si>
     <t>Maps</t>
+  </si>
+  <si>
+    <t>Hardship</t>
+  </si>
+  <si>
+    <t>Realm of the grafted King</t>
+  </si>
+  <si>
+    <t>Weeping Peninsula</t>
+  </si>
+  <si>
+    <t>Stormveil Castle</t>
+  </si>
+  <si>
+    <t>Limgrave Depths</t>
+  </si>
+  <si>
+    <t>Flora Material</t>
+  </si>
+  <si>
+    <t>Corpse Material</t>
+  </si>
+  <si>
+    <t>Ruins Material</t>
+  </si>
+  <si>
+    <t>Beast Material</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,13 +134,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -125,15 +164,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -412,222 +457,584 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
     <col min="4" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="14" width="9.140625" customWidth="1"/>
+    <col min="6" max="10" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1" customWidth="1"/>
+    <col min="12" max="14" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>61</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
+      <c r="D2">
+        <v>45</v>
+      </c>
+      <c r="F2">
+        <v>44</v>
+      </c>
+      <c r="H2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <f>B1-B2</f>
+      <c r="B4">
+        <f>B2-B3</f>
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
+      <c r="D4">
+        <f>D2-D3</f>
+        <v>42</v>
+      </c>
+      <c r="F4">
+        <f>F2-F3</f>
+        <v>41</v>
+      </c>
+      <c r="H4">
+        <f>H2-H3</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1">
+        <f>B6/$B$4</f>
+        <v>0.34545454545454546</v>
+      </c>
+      <c r="D6">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1">
+        <f>D6/$D$4</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1">
+        <f>F6/$F$4</f>
+        <v>0.43902439024390244</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6" s="1">
+        <f>H6/$H$4</f>
+        <v>0.32142857142857145</v>
+      </c>
+      <c r="J6">
+        <f>B6+D6+F6+H6</f>
+        <v>64</v>
+      </c>
+      <c r="K6" s="1">
+        <f>J6/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>0.38554216867469882</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1">
+        <f>B7/$B$4</f>
+        <v>0.14545454545454545</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1">
+        <f>D7/$D$4</f>
+        <v>0.26190476190476192</v>
+      </c>
+      <c r="F7">
         <v>7</v>
       </c>
-      <c r="C5" s="1">
-        <f>B5/$B$3</f>
+      <c r="G7" s="1">
+        <f>F7/$F$4</f>
+        <v>0.17073170731707318</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7" s="1">
+        <f>H7/$H$4</f>
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="J7">
+        <f>B7+D7+F7+H7</f>
+        <v>32</v>
+      </c>
+      <c r="K7" s="1">
+        <f>J7/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>0.19277108433734941</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1">
+        <f>B8/$B$4</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1">
+        <f>D8/$D$4</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1">
+        <f>F8/$F$4</f>
+        <v>0.12195121951219512</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8" s="1">
+        <f>H8/$H$4</f>
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="J8">
+        <f>B8+D8+F8+H8</f>
+        <v>27</v>
+      </c>
+      <c r="K8" s="1">
+        <f>J8/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>0.16265060240963855</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1">
+        <f>B9/$B$4</f>
+        <v>0.16363636363636364</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1">
+        <f>D9/$D$4</f>
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1">
+        <f>F9/$F$4</f>
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9" s="1">
+        <f>H9/$H$4</f>
+        <v>0.17857142857142858</v>
+      </c>
+      <c r="J9">
+        <f>B9+D9+F9+H9</f>
+        <v>27</v>
+      </c>
+      <c r="K9" s="1">
+        <f>J9/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>0.16265060240963855</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1">
+        <f>B10/$B$4</f>
+        <v>0.16363636363636364</v>
+      </c>
+      <c r="D10">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1">
+        <f>D10/$D$4</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1">
+        <f>F10/$F$4</f>
+        <v>0.12195121951219512</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <f>H10/$H$4</f>
+        <v>0.17857142857142858</v>
+      </c>
+      <c r="J10">
+        <f>B10+D10+F10+H10</f>
+        <v>26</v>
+      </c>
+      <c r="K10" s="1">
+        <f>J10/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>0.15662650602409639</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1">
+        <f>B11/$B$4</f>
+        <v>0.10909090909090909</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1">
+        <f>D11/$D$4</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <f>F11/$F$4</f>
+        <v>0.12195121951219512</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1">
+        <f>H11/$H$4</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="J11">
+        <f>B11+D11+F11+H11</f>
+        <v>20</v>
+      </c>
+      <c r="K11" s="1">
+        <f>J11/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>0.12048192771084337</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1">
+        <f>B12/$B$4</f>
         <v>0.12727272727272726</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1">
+        <f>D12/$D$4</f>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1">
+        <f>F12/$F$4</f>
+        <v>7.3170731707317069E-2</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1">
+        <f>H12/$H$4</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="J12">
+        <f>B12+D12+F12+H12</f>
+        <v>17</v>
+      </c>
+      <c r="K12" s="1">
+        <f>J12/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>0.10240963855421686</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1">
+        <f>B13/$B$4</f>
+        <v>0.10909090909090909</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1">
+        <f>D13/$D$4</f>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13" s="1">
+        <f>F13/$F$4</f>
+        <v>9.7560975609756101E-2</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1">
+        <f>H13/$H$4</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="J13">
+        <f>B13+D13+F13+H13</f>
+        <v>17</v>
+      </c>
+      <c r="K13" s="1">
+        <f>J13/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>0.10240963855421686</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1">
+        <f>B14/$B$4</f>
+        <v>0.10909090909090909</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1">
+        <f>D14/$D$4</f>
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" s="1">
+        <f>F14/$F$4</f>
+        <v>7.3170731707317069E-2</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14" s="1">
+        <f>H14/$H$4</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="J14">
+        <f>B14+D14+F14+H14</f>
+        <v>17</v>
+      </c>
+      <c r="K14" s="1">
+        <f>J14/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>0.10240963855421686</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <f>B15/$B$4</f>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1">
+        <f>D15/$D$4</f>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1">
+        <f>F15/$F$4</f>
+        <v>7.3170731707317069E-2</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15" s="1">
+        <f>H15/$H$4</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="J15">
+        <f>B15+D15+F15+H15</f>
+        <v>15</v>
+      </c>
+      <c r="K15" s="1">
+        <f>J15/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>9.036144578313253E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1">
+        <f>B16/$B$4</f>
+        <v>5.4545454545454543E-2</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1">
+        <f>D16/$D$4</f>
+        <v>9.5238095238095233E-2</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" s="1">
+        <f>F16/$F$4</f>
+        <v>0.12195121951219512</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16" s="1">
+        <f>H16/$H$4</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="J16">
+        <f>B16+D16+F16+H16</f>
+        <v>15</v>
+      </c>
+      <c r="K16" s="1">
+        <f>J16/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>9.036144578313253E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1">
+        <f>B17/$B$4</f>
+        <v>5.4545454545454543E-2</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <f>D17/$D$4</f>
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <f>F17/$F$4</f>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <f>H17/$H$4</f>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="J17">
+        <f>B17+D17+F17+H17</f>
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
-        <f>B6/$B$3</f>
-        <v>0.10909090909090909</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <f t="shared" ref="C7:C19" si="0">B7/$B$3</f>
-        <v>0.10909090909090909</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1">
-        <f>B8/$B$3</f>
-        <v>0.10909090909090909</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <f t="shared" si="0"/>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1">
-        <f t="shared" si="0"/>
-        <v>5.4545454545454543E-2</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1">
-        <f>B11/$B$3</f>
-        <v>5.4545454545454543E-2</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1">
-        <f t="shared" si="0"/>
-        <v>3.6363636363636362E-2</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1">
-        <f t="shared" si="0"/>
-        <v>3.6363636363636362E-2</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1">
-        <f t="shared" si="0"/>
-        <v>3.6363636363636362E-2</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15" s="1">
-        <f t="shared" si="0"/>
-        <v>3.6363636363636362E-2</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16" s="1">
-        <f t="shared" si="0"/>
-        <v>3.6363636363636362E-2</v>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1">
-        <f t="shared" si="0"/>
-        <v>3.6363636363636362E-2</v>
-      </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K17" s="1">
+        <f>J17/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>4.2168674698795178E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -635,41 +1042,377 @@
         <v>2</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" si="0"/>
+        <f>B18/$B$4</f>
         <v>3.6363636363636362E-2</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <f>D18/$D$4</f>
+        <v>2.3809523809523808E-2</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <f>F18/$F$4</f>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1">
+        <f>H18/$H$4</f>
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="J18">
+        <f>B18+D18+F18+H18</f>
+        <v>6</v>
+      </c>
+      <c r="K18" s="1">
+        <f>J18/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>3.614457831325301E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" si="0"/>
+        <f>B19/$B$4</f>
         <v>3.6363636363636362E-2</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <f>D19/$D$4</f>
+        <v>2.3809523809523808E-2</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <f>F19/$F$4</f>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <f>H19/$H$4</f>
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <f>B19+D19+F19+H19</f>
+        <v>4</v>
+      </c>
+      <c r="K19" s="1">
+        <f>J19/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>2.4096385542168676E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1">
+        <f>B20/$B$4</f>
+        <v>3.6363636363636362E-2</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <f>D20/$D$4</f>
+        <v>2.3809523809523808E-2</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <f>F20/$F$4</f>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <f>H20/$H$4</f>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <f>B20+D20+F20+H20</f>
+        <v>4</v>
+      </c>
+      <c r="K20" s="1">
+        <f>J20/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>2.4096385542168676E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>6</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1">
-        <f>B20/$B$3</f>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
+        <f>B21/$B$4</f>
         <v>1.8181818181818181E-2</v>
       </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <f>D21/$D$4</f>
+        <v>2.3809523809523808E-2</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <f>F21/$F$4</f>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <f>H21/$H$4</f>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="J21">
+        <f>B21+D21+F21+H21</f>
+        <v>4</v>
+      </c>
+      <c r="K21" s="1">
+        <f>J21/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>2.4096385542168676E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" s="1">
+        <f>B22/$B$4</f>
+        <v>3.6363636363636362E-2</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <f>D22/$D$4</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <f>F22/$F$4</f>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
+        <f>H22/$H$4</f>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="J22">
+        <f>B22+D22+F22+H22</f>
+        <v>3</v>
+      </c>
+      <c r="K22" s="1">
+        <f>J22/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>1.8072289156626505E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1">
+        <f>B23/$B$4</f>
+        <v>3.6363636363636362E-2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4">
+        <f>D23/$D$4</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4">
+        <f>F23/$F$4</f>
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
+        <f>H23/$H$4</f>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="J23">
+        <f>B23+D23+F23+H23</f>
+        <v>3</v>
+      </c>
+      <c r="K23" s="1">
+        <f>J23/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>1.8072289156626505E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1">
+        <f>B24/$B$4</f>
+        <v>3.6363636363636362E-2</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <f>D24/$D$4</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f>F24/$F$4</f>
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
+        <f>H24/$H$4</f>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="J24">
+        <f>B24+D24+F24+H24</f>
+        <v>3</v>
+      </c>
+      <c r="K24" s="1">
+        <f>J24/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>1.8072289156626505E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1">
+        <f>B25/$B$4</f>
+        <v>3.6363636363636362E-2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4">
+        <f>D25/$D$4</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4">
+        <f>F25/$F$4</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4">
+        <f>H25/$H$4</f>
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <f>B25+D25+F25+H25</f>
+        <v>2</v>
+      </c>
+      <c r="K25" s="1">
+        <f>J25/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>1.2048192771084338E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26" s="1">
+        <f>B26/$B$4</f>
+        <v>3.6363636363636362E-2</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4">
+        <f>D26/$D$4</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4">
+        <f>F26/$F$4</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4">
+        <f>H26/$H$4</f>
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <f>B26+D26+F26+H26</f>
+        <v>2</v>
+      </c>
+      <c r="K26" s="1">
+        <f>J26/($B$4+$D$4+$F$4+$H$4)</f>
+        <v>1.2048192771084338E-2</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:K28">
+    <sortCondition descending="1" ref="J6:J28"/>
+  </sortState>
+  <mergeCells count="4">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>